--- a/reports/booking_report.xlsx
+++ b/reports/booking_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -465,32 +465,370 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Run_20261001_155049</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>440473</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Saudi-United States</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:51:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Run_20261001_155049</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>B2C Pallet (Web)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>631015</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>689411</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>India-Saudi</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:51:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Run_20261001_161009</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>896590</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Saudi-United States</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fedex Express</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Requested</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:12:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Run_20261002_140109</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>454559</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Saudi-France</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-10-02 14:01:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Run_20261002_140109</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>399006</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Australia-Saudi</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fedex</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-10-02 14:01:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Run_20261002_140240</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>586217</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Saudi-France</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Fedex Priority</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Requested</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-10-02 14:03:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Run_20261002_140240</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>564526</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>United States-Saudi</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fedex Express</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Shipment Submitted</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-09-23 11:44:59</t>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-10-02 14:03:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Run_20261002_153557</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1032652</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Germany-Saudi</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Fedex Connect Plus</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-10-02 15:39:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Run_20261002_154415</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>398381</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Saudi-France</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-10-02 15:44:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Run_20261002_172739</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>759691</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Saudi-France</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-10-02 17:29:12</t>
         </is>
       </c>
     </row>

--- a/reports/booking_report.xlsx
+++ b/reports/booking_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -832,6 +832,154 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Run_20261002_174412</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1170679</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Saudi-Germany</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-10-02 17:44:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Run_20261002_174412</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>676677</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>France-Saudi</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-10-02 17:44:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Run_20261002_174640</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>757337</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Saudi-France</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-10-02 17:46:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Run_20261002_174640</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1033294</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>China-Saudi</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-10-02 17:47:04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/booking_report.xlsx
+++ b/reports/booking_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -980,6 +980,228 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Run_20261005_113545</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>413929</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Spain-Saudi</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:37:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Run_20261005_113907</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1060286</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Saudi-India</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:39:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Run_20261005_122106</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>280814</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Saudi-Bangladesh</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:21:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Run_20261005_122106</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>535907</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>China-Saudi</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Run_20261005_154202</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1155113</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Saudi-China</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:43:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Run_20261005_154202</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>286082</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>United States-Saudi</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:43:43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/booking_report.xlsx
+++ b/reports/booking_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1202,6 +1202,228 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Run_20261005_183505</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1147334</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Saudi-India</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-10-05 18:37:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Run_20261005_183505</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>792081</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>France-Saudi</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-10-05 18:37:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Run_20261006_152238</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>517963</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Saudi-Brazil</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:24:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Run_20261006_152238</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>407132</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Germany-Saudi</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:24:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Run_20261006_153700</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>396623</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Saudi-India</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Run_20261006_153700</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>726499</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>United States-Saudi</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:37:23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/booking_report.xlsx
+++ b/reports/booking_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1424,6 +1424,228 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Run_20261006_161303</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>615062</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Saudi-Singapore</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Fedex Priority</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Requested</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:13:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Run_20261007_154647</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1051915</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Saudi-أفغانستان</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:46:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Run_20261007_154647</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>540161</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Afghanistan-Saudi</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>DHL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Requested</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:47:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Run_20261007_155504</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>857661</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Saudi-India</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Fedex Express</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Requested</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:55:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Run_20261007_160730</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>823084</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Saudi-China</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Fedex Connect Plus</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Requested</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-10-07 16:08:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Run_20261007_160730</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>905591</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>United States-Saudi</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Darb</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-10-07 16:08:25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/booking_report.xlsx
+++ b/reports/booking_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1646,6 +1646,265 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Run_20261008_163319</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1137205</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Saudi-Ethiopia</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:35:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Run_20261008_163319</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>942201</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>France-Saudi</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:35:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Run_20261008_163911</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>806106</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Saudi-India</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:39:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Run_20261008_164002</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>888398</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Saudi-France</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:40:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Run_20261008_164107</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>505601</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Saudi-Spain</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:41:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Run_20261008_164226</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>325263</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Saudi-Australia</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:42:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Run_20261008_170844</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>396601</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Saudi-Vietnam</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-10-08 17:08:55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/booking_report.xlsx
+++ b/reports/booking_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1905,6 +1905,487 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Run_20261008_171723</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>419446</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Saudi-India</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-10-08 17:17:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Run_20261009_165337</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>308475</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Saudi-Austria</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:55:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Run_20261009_170137</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>905374</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Saudi-France</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:01:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Run_20261009_170137</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>653662</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Germany-Saudi</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Run_20261009_170353</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1072772</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Saudi-Germany</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:04:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Run_20261009_170353</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>831749</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>United States-Saudi</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:04:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Run_20261009_171049</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>806866</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Germany-Saudi</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:11:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Run_20261009_171222</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>604477</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Saudi-United States</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Run_20261009_171222</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>290739</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>India-Saudi</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:12:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Run_20261009_171520</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>300596</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Saudi-Australia</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:15:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Run_20261009_171520</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>665117</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>China-Saudi</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Run_20261009_171854</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>442020</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Saudi-United Kingdom</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Run_20261009_171854</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>855717</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>United States-Saudi</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:19:20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/booking_report.xlsx
+++ b/reports/booking_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2386,6 +2386,302 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Run_20261012_115023</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Saudi-India</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Fedex</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SKIPPED: no price at add (ppd_amount=None)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:51:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Run_20261012_115023</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>637979</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Argentina-Saudi</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:51:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Run_20261012_115541</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>663966</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Saudi-Spain</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:55:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Run_20261012_115541</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>355950</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Greece-Saudi</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:56:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Run_20261012_120846</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>828590</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Saudi-Germany</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:08:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Run_20261012_120846</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1017733</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Uganda-Saudi</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:09:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Run_20261012_121017</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>408350</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Saudi-Australia</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Run_20261012_121017</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>949324</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>France-Saudi</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:10:40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/booking_report.xlsx
+++ b/reports/booking_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2682,6 +2682,302 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Run_20261012_152841</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1108959</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Saudi-Myanmar (Burma)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:30:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Run_20261012_152841</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>706543</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>France-Saudi</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:30:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Run_20261013_115424</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>742159</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Saudi-Armenia</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:56:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Run_20261013_115424</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>864227</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Belgium-Saudi</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aramex</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:56:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Run_20261013_120025</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Saudi-Indonesia</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>DHL Express Easy</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SKIPPED: no price at add (ppd_amount=None)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:00:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Run_20261013_120025</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Saudi-Niger</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Fedex</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SKIPPED: no price at add (ppd_amount=None)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Run_20261013_120025</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>B2C Parcel (Web)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Saudi-Ukraine</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>DHL Express Worldwide</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SKIPPED: no price at add (ppd_amount=None)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Run_20261013_120025</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>B2C Pallet (Web)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1056663</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Russia-Saudi</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Shipment Submitted</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:00:55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
